--- a/fhir/ig/cl-urgencia/0.2.0/StructureDefinition-encuentro-urgencia.xlsx
+++ b/fhir/ig/cl-urgencia/0.2.0/StructureDefinition-encuentro-urgencia.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3458" uniqueCount="584">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3458" uniqueCount="586">
   <si>
     <t>Property</t>
   </si>
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://interoperabilidad.minsal.cl/fhir/ig/urgencia/StructureDefinition/encuentro-urgencia</t>
+    <t>https://interoperabilidad.minsal.cl/fhir/ig/urgencia-eventos/StructureDefinition/encuentro-urgencia</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T16:36:45-03:00</t>
+    <t>2026-09-24T11:47:41-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -266,7 +266,7 @@
 </t>
   </si>
   <si>
-    <t>An interaction during which services are provided to the patient</t>
+    <t>Episodio de atención de urgencia</t>
   </si>
   <si>
     <t>An interaction between a patient and healthcare provider(s) for the purpose of providing healthcare service(s) or assessing the health status of a patient.</t>
@@ -433,7 +433,7 @@
 </t>
   </si>
   <si>
-    <t>Extension</t>
+    <t>Datos del CMBD sin elemento FHIR (previsión, leyes, clasificación, pronóstico, pertinencia)</t>
   </si>
   <si>
     <t>An Extension</t>
@@ -459,7 +459,7 @@
     <t>prevision</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interoperabilidad.minsal.cl/fhir/ig/urgencia/StructureDefinition/prevision}
+    <t xml:space="preserve">Extension {https://interoperabilidad.minsal.cl/fhir/ig/urgencia-eventos/StructureDefinition/prevision}
 </t>
   </si>
   <si>
@@ -479,7 +479,7 @@
     <t>leyPrevisional</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interoperabilidad.minsal.cl/fhir/ig/urgencia/StructureDefinition/ley-previsional}
+    <t xml:space="preserve">Extension {https://interoperabilidad.minsal.cl/fhir/ig/urgencia-eventos/StructureDefinition/ley-previsional}
 </t>
   </si>
   <si>
@@ -495,7 +495,7 @@
     <t>clasificacionConsulta</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interoperabilidad.minsal.cl/fhir/ig/urgencia/StructureDefinition/clasificacion-consulta}
+    <t xml:space="preserve">Extension {https://interoperabilidad.minsal.cl/fhir/ig/urgencia-eventos/StructureDefinition/clasificacion-consulta}
 </t>
   </si>
   <si>
@@ -511,7 +511,7 @@
     <t>pronosticoMedicoLegal</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interoperabilidad.minsal.cl/fhir/ig/urgencia/StructureDefinition/pronostico-medico-legal}
+    <t xml:space="preserve">Extension {https://interoperabilidad.minsal.cl/fhir/ig/urgencia-eventos/StructureDefinition/pronostico-medico-legal}
 </t>
   </si>
   <si>
@@ -527,7 +527,7 @@
     <t>pertinencia</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interoperabilidad.minsal.cl/fhir/ig/urgencia/StructureDefinition/pertinencia}
+    <t xml:space="preserve">Extension {https://interoperabilidad.minsal.cl/fhir/ig/urgencia-eventos/StructureDefinition/pertinencia}
 </t>
   </si>
   <si>
@@ -686,7 +686,7 @@
     <t>Encounter.identifier.system</t>
   </si>
   <si>
-    <t>The namespace for the identifier value</t>
+    <t>Sistema del ID DAU; identifica al establecimiento</t>
   </si>
   <si>
     <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
@@ -713,7 +713,7 @@
     <t>Encounter.identifier.value</t>
   </si>
   <si>
-    <t>The value that is unique</t>
+    <t>ID DAU</t>
   </si>
   <si>
     <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
@@ -793,7 +793,7 @@
     <t>Note that internal business rules will determine the appropriate transitions that may occur between statuses (and also classes).</t>
   </si>
   <si>
-    <t>https://interoperabilidad.minsal.cl/fhir/ig/urgencia/ValueSet/vs-estado-encuentro-urgencia</t>
+    <t>https://interoperabilidad.minsal.cl/fhir/ig/urgencia-eventos/ValueSet/vs-estado-encuentro-urgencia</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -876,6 +876,9 @@
   <si>
     <t xml:space="preserve">Coding
 </t>
+  </si>
+  <si>
+    <t>Clase de encuentro: EMER (urgencia)</t>
   </si>
   <si>
     <t>Clasificación del encuentro con el paciente</t>
@@ -977,7 +980,7 @@
     <t>Categorización del servicio que se va a prestar en el encuentro (por ejemplo, servicio de Ginecología)</t>
   </si>
   <si>
-    <t>https://interoperabilidad.minsal.cl/fhir/ig/urgencia/ValueSet/vs-unidad-atencion</t>
+    <t>https://interoperabilidad.minsal.cl/fhir/ig/urgencia-eventos/ValueSet/vs-unidad-atencion</t>
   </si>
   <si>
     <t>PV1-10</t>
@@ -1015,7 +1018,7 @@
 </t>
   </si>
   <si>
-    <t>Referencia al paciente del encuentro</t>
+    <t>Paciente atendido</t>
   </si>
   <si>
     <t>La referencia al paciente que está presente en el encuentro clínico sobre un paciente nacional.</t>
@@ -1154,7 +1157,7 @@
 </t>
   </si>
   <si>
-    <t>Referencia al participante</t>
+    <t>Profesional</t>
   </si>
   <si>
     <t>Persons involved in the encounter other than the patient.</t>
@@ -1194,6 +1197,9 @@
     <t>Encounter.period</t>
   </si>
   <si>
+    <t>Inicio (admisión) y término (alta o abandono) del episodio</t>
+  </si>
+  <si>
     <t>La hora de inicio y finalización del encuentro</t>
   </si>
   <si>
@@ -1357,7 +1363,7 @@
     <t>Encounter.reasonCode.text</t>
   </si>
   <si>
-    <t>Plain text representation of the concept</t>
+    <t>Motivo de consulta en texto libre</t>
   </si>
   <si>
     <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
@@ -1441,13 +1447,13 @@
     <t>Encounter.diagnosis.use</t>
   </si>
   <si>
-    <t>Role that this diagnosis has within the encounter (e.g. admission, billing, discharge …)</t>
+    <t>AD (hipótesis de ingreso) | DD (diagnóstico de egreso)</t>
   </si>
   <si>
     <t>Role that this diagnosis has within the encounter (e.g. admission, billing, discharge …).</t>
   </si>
   <si>
-    <t>https://interoperabilidad.minsal.cl/fhir/ig/urgencia/ValueSet/vs-uso-diagnostico</t>
+    <t>https://interoperabilidad.minsal.cl/fhir/ig/urgencia-eventos/ValueSet/vs-uso-diagnostico</t>
   </si>
   <si>
     <t>Encounter.diagnosis.rank</t>
@@ -1457,7 +1463,7 @@
 </t>
   </si>
   <si>
-    <t>Ranking of the diagnosis (for each role type)</t>
+    <t>Orden del diagnóstico (1 = principal)</t>
   </si>
   <si>
     <t>Ranking of the diagnosis (for each role type).</t>
@@ -1488,7 +1494,7 @@
     <t>Encounter.hospitalization</t>
   </si>
   <si>
-    <t>Details about the admission to a healthcare service</t>
+    <t>Datos de llegada y egreso de la urgencia</t>
   </si>
   <si>
     <t>Details about the admission to a healthcare service.</t>
@@ -1508,17 +1514,17 @@
     <t>Encounter.hospitalization.extension</t>
   </si>
   <si>
+    <t>Medio de llegada</t>
+  </si>
+  <si>
     <t>Encounter.hospitalization.extension:medioLlegada</t>
   </si>
   <si>
     <t>medioLlegada</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interoperabilidad.minsal.cl/fhir/ig/urgencia/StructureDefinition/medio-llegada}
+    <t xml:space="preserve">Extension {https://interoperabilidad.minsal.cl/fhir/ig/urgencia-eventos/StructureDefinition/medio-llegada}
 </t>
-  </si>
-  <si>
-    <t>Medio de llegada</t>
   </si>
   <si>
     <t>Medio de transporte con que el paciente llega a la unidad de urgencia.</t>
@@ -1564,7 +1570,7 @@
     <t>From where patient was admitted (physician referral, transfer).</t>
   </si>
   <si>
-    <t>https://interoperabilidad.minsal.cl/fhir/ig/urgencia/ValueSet/vs-procedencia</t>
+    <t>https://interoperabilidad.minsal.cl/fhir/ig/urgencia-eventos/ValueSet/vs-procedencia</t>
   </si>
   <si>
     <t>.admissionReferralSourceCode</t>
@@ -1684,7 +1690,7 @@
     <t>Category or kind of location after discharge.</t>
   </si>
   <si>
-    <t>https://interoperabilidad.minsal.cl/fhir/ig/urgencia/ValueSet/vs-destino-egreso</t>
+    <t>https://interoperabilidad.minsal.cl/fhir/ig/urgencia-eventos/ValueSet/vs-destino-egreso</t>
   </si>
   <si>
     <t>.dischargeDispositionCode</t>
@@ -1795,7 +1801,7 @@
 </t>
   </si>
   <si>
-    <t>La organización (instalación) responsable de este encuentro</t>
+    <t>Establecimiento que realiza la atención</t>
   </si>
   <si>
     <t>The organization that is primarily responsible for this Encounter's services. This MAY be the same as the organization on the Patient record, however it could be different, such as if the actor performing the services was from an external organization (which may be billed seperately) for an external consultation.  Refer to the example bundle showing an abbreviated set of Encounters for a colonoscopy.</t>
@@ -2158,7 +2164,7 @@
     <col min="8" max="8" width="12.6875" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="10.51171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="85.859375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="92.05859375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2173,7 +2179,7 @@
     <col min="23" max="23" width="15.01171875" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="82.29296875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="72.76171875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="79.609375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.07421875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="17.98046875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="34.578125" customWidth="true" bestFit="true"/>
@@ -5753,7 +5759,7 @@
         <v>276</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5765,7 +5771,7 @@
         <v>80</v>
       </c>
       <c r="S32" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="T32" t="s" s="2">
         <v>80</v>
@@ -5784,7 +5790,7 @@
       </c>
       <c r="Y32" s="2"/>
       <c r="Z32" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>80</v>
@@ -5820,21 +5826,21 @@
         <v>80</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5860,10 +5866,10 @@
         <v>255</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5914,7 +5920,7 @@
         <v>80</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5943,10 +5949,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6055,10 +6061,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6169,10 +6175,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6285,10 +6291,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6314,10 +6320,10 @@
         <v>275</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6347,10 +6353,10 @@
         <v>208</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>80</v>
@@ -6368,7 +6374,7 @@
         <v>80</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>88</v>
@@ -6397,10 +6403,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6426,10 +6432,10 @@
         <v>231</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6480,7 +6486,7 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>88</v>
@@ -6509,10 +6515,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6538,13 +6544,13 @@
         <v>203</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6570,11 +6576,11 @@
         <v>80</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Y39" s="2"/>
       <c r="Z39" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>80</v>
@@ -6592,7 +6598,7 @@
         <v>80</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6607,24 +6613,24 @@
         <v>100</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6650,10 +6656,10 @@
         <v>203</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6684,7 +6690,7 @@
       </c>
       <c r="Y40" s="2"/>
       <c r="Z40" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>80</v>
@@ -6702,7 +6708,7 @@
         <v>80</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6717,7 +6723,7 @@
         <v>100</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>186</v>
@@ -6726,15 +6732,15 @@
         <v>80</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6760,10 +6766,10 @@
         <v>203</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6790,13 +6796,13 @@
         <v>80</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>80</v>
@@ -6814,7 +6820,7 @@
         <v>80</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6832,25 +6838,25 @@
         <v>80</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6869,16 +6875,16 @@
         <v>89</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6928,7 +6934,7 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6943,24 +6949,24 @@
         <v>100</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6983,13 +6989,13 @@
         <v>89</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7040,7 +7046,7 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -7055,28 +7061,28 @@
         <v>100</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>186</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7095,13 +7101,13 @@
         <v>80</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7152,7 +7158,7 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -7167,10 +7173,10 @@
         <v>100</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>80</v>
@@ -7181,10 +7187,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7210,10 +7216,10 @@
         <v>255</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7264,7 +7270,7 @@
         <v>80</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -7279,24 +7285,24 @@
         <v>100</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7405,10 +7411,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7519,10 +7525,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7635,10 +7641,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7664,13 +7670,13 @@
         <v>203</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7700,7 +7706,7 @@
       </c>
       <c r="Y49" s="2"/>
       <c r="Z49" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>80</v>
@@ -7718,7 +7724,7 @@
         <v>80</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7733,24 +7739,24 @@
         <v>100</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7776,10 +7782,10 @@
         <v>231</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7830,7 +7836,7 @@
         <v>80</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7848,21 +7854,21 @@
         <v>80</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7885,13 +7891,13 @@
         <v>89</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7942,7 +7948,7 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7957,24 +7963,24 @@
         <v>100</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7997,13 +8003,13 @@
         <v>89</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8054,7 +8060,7 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -8069,24 +8075,24 @@
         <v>100</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8112,13 +8118,13 @@
         <v>231</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8168,7 +8174,7 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -8183,24 +8189,24 @@
         <v>100</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8309,10 +8315,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8423,10 +8429,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8449,16 +8455,16 @@
         <v>89</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8508,7 +8514,7 @@
         <v>80</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8517,7 +8523,7 @@
         <v>88</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>100</v>
@@ -8526,21 +8532,21 @@
         <v>80</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8563,23 +8569,23 @@
         <v>89</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q57" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="R57" t="s" s="2">
         <v>80</v>
@@ -8624,7 +8630,7 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -8633,7 +8639,7 @@
         <v>88</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>100</v>
@@ -8642,21 +8648,21 @@
         <v>80</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8679,16 +8685,16 @@
         <v>80</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8738,7 +8744,7 @@
         <v>80</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8753,28 +8759,28 @@
         <v>100</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -8796,13 +8802,13 @@
         <v>203</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -8831,10 +8837,10 @@
         <v>112</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>80</v>
@@ -8852,7 +8858,7 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -8867,24 +8873,24 @@
         <v>100</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8993,10 +8999,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9107,10 +9113,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9136,16 +9142,16 @@
         <v>275</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>80</v>
@@ -9194,7 +9200,7 @@
         <v>80</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -9212,21 +9218,21 @@
         <v>80</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9252,16 +9258,16 @@
         <v>182</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>80</v>
@@ -9310,7 +9316,7 @@
         <v>80</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -9328,25 +9334,25 @@
         <v>80</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -9365,16 +9371,16 @@
         <v>89</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9424,7 +9430,7 @@
         <v>80</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -9439,24 +9445,24 @@
         <v>100</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9482,10 +9488,10 @@
         <v>255</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9536,7 +9542,7 @@
         <v>80</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -9554,7 +9560,7 @@
         <v>80</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>80</v>
@@ -9565,10 +9571,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9677,10 +9683,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9791,10 +9797,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9907,14 +9913,14 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -9933,16 +9939,16 @@
         <v>89</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -9992,7 +9998,7 @@
         <v>80</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>88</v>
@@ -10007,24 +10013,24 @@
         <v>100</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10050,10 +10056,10 @@
         <v>203</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10084,7 +10090,7 @@
       </c>
       <c r="Y70" s="2"/>
       <c r="Z70" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>80</v>
@@ -10102,7 +10108,7 @@
         <v>80</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -10131,10 +10137,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10157,13 +10163,13 @@
         <v>80</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10214,7 +10220,7 @@
         <v>80</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -10232,7 +10238,7 @@
         <v>80</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>80</v>
@@ -10243,10 +10249,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10269,16 +10275,16 @@
         <v>80</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10328,7 +10334,7 @@
         <v>80</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -10346,7 +10352,7 @@
         <v>80</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>80</v>
@@ -10357,10 +10363,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10386,13 +10392,13 @@
         <v>255</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10442,7 +10448,7 @@
         <v>80</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -10460,7 +10466,7 @@
         <v>80</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>80</v>
@@ -10471,10 +10477,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10583,10 +10589,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10612,7 +10618,7 @@
         <v>133</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>134</v>
+        <v>481</v>
       </c>
       <c r="M75" t="s" s="2">
         <v>135</v>
@@ -10693,13 +10699,13 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C76" t="s" s="2">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="D76" t="s" s="2">
         <v>80</v>
@@ -10721,13 +10727,13 @@
         <v>80</v>
       </c>
       <c r="K76" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="L76" t="s" s="2">
         <v>481</v>
       </c>
-      <c r="L76" t="s" s="2">
-        <v>482</v>
-      </c>
       <c r="M76" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -10807,10 +10813,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10923,10 +10929,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10952,10 +10958,10 @@
         <v>174</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11006,7 +11012,7 @@
         <v>80</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -11030,15 +11036,15 @@
         <v>80</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11061,13 +11067,13 @@
         <v>80</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11118,7 +11124,7 @@
         <v>80</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -11136,7 +11142,7 @@
         <v>80</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>80</v>
@@ -11147,10 +11153,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11176,10 +11182,10 @@
         <v>203</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11210,7 +11216,7 @@
       </c>
       <c r="Y80" s="2"/>
       <c r="Z80" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>80</v>
@@ -11228,7 +11234,7 @@
         <v>80</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
@@ -11246,21 +11252,21 @@
         <v>80</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11286,10 +11292,10 @@
         <v>203</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -11316,13 +11322,13 @@
         <v>80</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>80</v>
@@ -11340,7 +11346,7 @@
         <v>80</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
@@ -11364,15 +11370,15 @@
         <v>80</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11398,16 +11404,16 @@
         <v>203</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>80</v>
@@ -11432,13 +11438,13 @@
         <v>80</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>80</v>
@@ -11456,7 +11462,7 @@
         <v>80</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
@@ -11474,21 +11480,21 @@
         <v>80</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11514,10 +11520,10 @@
         <v>203</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -11547,10 +11553,10 @@
         <v>112</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>80</v>
@@ -11568,7 +11574,7 @@
         <v>80</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
@@ -11586,21 +11592,21 @@
         <v>80</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11626,10 +11632,10 @@
         <v>203</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -11659,10 +11665,10 @@
         <v>112</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>80</v>
@@ -11680,7 +11686,7 @@
         <v>80</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
@@ -11698,21 +11704,21 @@
         <v>80</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11735,13 +11741,13 @@
         <v>80</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -11792,7 +11798,7 @@
         <v>80</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
@@ -11810,21 +11816,21 @@
         <v>80</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11850,10 +11856,10 @@
         <v>203</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -11884,7 +11890,7 @@
       </c>
       <c r="Y86" s="2"/>
       <c r="Z86" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>80</v>
@@ -11902,7 +11908,7 @@
         <v>80</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
@@ -11920,21 +11926,21 @@
         <v>80</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11960,13 +11966,13 @@
         <v>255</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -12016,7 +12022,7 @@
         <v>80</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>78</v>
@@ -12034,7 +12040,7 @@
         <v>80</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>80</v>
@@ -12045,10 +12051,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12157,10 +12163,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12271,10 +12277,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12387,10 +12393,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12413,13 +12419,13 @@
         <v>80</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -12470,7 +12476,7 @@
         <v>80</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>88</v>
@@ -12485,24 +12491,24 @@
         <v>100</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12528,13 +12534,13 @@
         <v>108</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -12563,10 +12569,10 @@
         <v>197</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>80</v>
@@ -12584,7 +12590,7 @@
         <v>80</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>78</v>
@@ -12602,7 +12608,7 @@
         <v>80</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>80</v>
@@ -12613,10 +12619,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12642,13 +12648,13 @@
         <v>203</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -12674,13 +12680,13 @@
         <v>80</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>80</v>
@@ -12698,7 +12704,7 @@
         <v>80</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
@@ -12727,10 +12733,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12756,10 +12762,10 @@
         <v>231</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -12810,7 +12816,7 @@
         <v>80</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
@@ -12828,7 +12834,7 @@
         <v>80</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>80</v>
@@ -12839,10 +12845,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12865,13 +12871,13 @@
         <v>80</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -12922,7 +12928,7 @@
         <v>80</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>78</v>
@@ -12937,24 +12943,24 @@
         <v>100</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -12977,16 +12983,16 @@
         <v>80</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -13036,7 +13042,7 @@
         <v>80</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>78</v>
@@ -13051,10 +13057,10 @@
         <v>100</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>80</v>

--- a/fhir/ig/cl-urgencia/0.2.0/StructureDefinition-encuentro-urgencia.xlsx
+++ b/fhir/ig/cl-urgencia/0.2.0/StructureDefinition-encuentro-urgencia.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$96</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$104</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3458" uniqueCount="586">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3745" uniqueCount="624">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-24T11:47:41-03:00</t>
+    <t>2026-10-08T00:02:21-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -269,11 +269,11 @@
     <t>Episodio de atención de urgencia</t>
   </si>
   <si>
-    <t>An interaction between a patient and healthcare provider(s) for the purpose of providing healthcare service(s) or assessing the health status of a patient.</t>
+    <t>Episodio de atención en una unidad de urgencia. Se envía SIEMPRE COMPLETO en cada evento: el PUT condicional reemplaza el recurso entero, por lo que el alta y el abandono deben repetir todos los datos informados en la admisión (previsión, procedencia, medio de llegada, motivo de consulta, etc.). Un dato omitido en el alta se borra del repositorio.</t>
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}urg-enc-1:Un episodio finalizado debe informar la fecha y hora de término (period.end). {status = 'finished' implies period.end.exists()}urg-enc-2:Un episodio finalizado debe informar el destino de egreso o el tipo de abandono. {status = 'finished' implies hospitalization.dischargeDisposition.exists()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}urg-enc-1:Un episodio finalizado debe informar la fecha y hora de término (period.end). {status = 'finished' implies period.end.exists()}urg-enc-2:Un episodio finalizado debe informar el destino de egreso o el tipo de abandono. {status = 'finished' implies hospitalization.dischargeDisposition.exists()}urg-enc-3:La fecha y hora de término (alta o abandono) no puede ser anterior a la de admisión. {period.end.exists() implies period.end &gt;= period.start}urg-enc-4:Solo los diagnósticos de egreso (DD) se informan con uso; las hipótesis del abandono van sin uso. {diagnosis.use.exists() implies diagnosis.use.coding.all(code = 'DD')}urg-enc-5:Las fechas de admisión, alta y abandono deben incluir hora (con zona horaria), no solo la fecha. {period.start.toString().contains('T') and (period.end.exists() implies period.end.toString().contains('T'))}urg-enc-6:El episodio debe tener exactamente un ID DAU, con sistema https://interoperabilidad.minsal.cl/fhir/sid/dau/[código DEIS del establecimiento]. {identifier.where(system.startsWith('https://interoperabilidad.minsal.cl/fhir/sid/dau/')).count() = 1}urg-enc-7:Si la consulta se clasifica como abuso sexual (01), maltrato o violencia de género (02) o constatación de lesiones (03), el episodio debe marcarse como restringido (meta.security = R). {extension.where(url = 'https://interoperabilidad.minsal.cl/fhir/ig/urgencia-eventos/StructureDefinition/clasificacion-consulta').value.ofType(CodeableConcept).coding.where(code = '01' or code = '02' or code = '03').exists() implies meta.security.where(system = 'http://terminology.hl7.org/CodeSystem/v3-Confidentiality' and code = 'R').exists()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -327,13 +327,190 @@
 </t>
   </si>
   <si>
-    <t>Encounter.implicitRules</t>
+    <t>Encounter.meta.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Encounter.meta.extension</t>
+  </si>
+  <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>Encounter.meta.versionId</t>
+  </si>
+  <si>
+    <t>Version specific identifier</t>
+  </si>
+  <si>
+    <t>The version specific identifier, as it appears in the version portion of the URL. This value changes when the resource is created, updated, or deleted.</t>
+  </si>
+  <si>
+    <t>The server assigns this value, and ignores what the client specifies, except in the case that the server is imposing version integrity on updates/deletes.</t>
+  </si>
+  <si>
+    <t>Meta.versionId</t>
+  </si>
+  <si>
+    <t>Encounter.meta.lastUpdated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instant
+</t>
+  </si>
+  <si>
+    <t>When the resource version last changed</t>
+  </si>
+  <si>
+    <t>When the resource last changed - e.g. when the version changed.</t>
+  </si>
+  <si>
+    <t>This value is always populated except when the resource is first being created. The server / resource manager sets this value; what a client provides is irrelevant. This is equivalent to the HTTP Last-Modified and SHOULD have the same value on a [read](http://hl7.org/fhir/R4/http.html#read) interaction.</t>
+  </si>
+  <si>
+    <t>Meta.lastUpdated</t>
+  </si>
+  <si>
+    <t>Encounter.meta.source</t>
   </si>
   <si>
     <t xml:space="preserve">uri
 </t>
   </si>
   <si>
+    <t>Identifies where the resource comes from</t>
+  </si>
+  <si>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+  </si>
+  <si>
+    <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
+This element can be used to indicate where the current master source of a resource that has a canonical URL if the resource is no longer hosted at the canonical URL.</t>
+  </si>
+  <si>
+    <t>Meta.source</t>
+  </si>
+  <si>
+    <t>Encounter.meta.profile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Profiles this resource claims to conform to</t>
+  </si>
+  <si>
+    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
+  </si>
+  <si>
+    <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
+  </si>
+  <si>
+    <t>Meta.profile</t>
+  </si>
+  <si>
+    <t>Encounter.meta.security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>R (restringido) si la consulta es por abuso sexual, violencia o constatación de lesiones</t>
+  </si>
+  <si>
+    <t>Security labels applied to this resource. These tags connect specific resources to the overall security policy and infrastructure.</t>
+  </si>
+  <si>
+    <t>The security labels can be updated without changing the stated version of the resource. The list of security labels is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
+  </si>
+  <si>
+    <t>Meta.security</t>
+  </si>
+  <si>
+    <t>Encounter.meta.tag</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource. Tags are intended to be used to identify and relate resources to process and workflow, and applications are not required to consider the tags when interpreting the meaning of a resource.</t>
+  </si>
+  <si>
+    <t>The tags can be updated without changing the stated version of the resource. The list of tags is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
+  </si>
+  <si>
+    <t>Meta.tag</t>
+  </si>
+  <si>
+    <t>Encounter.implicitRules</t>
+  </si>
+  <si>
     <t>A set of rules under which this content was created</t>
   </si>
   <si>
@@ -429,28 +606,13 @@
     <t>Encounter.extension</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
     <t>Datos del CMBD sin elemento FHIR (previsión, leyes, clasificación, pronóstico, pertinencia)</t>
   </si>
   <si>
     <t>An Extension</t>
   </si>
   <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
     <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Encounter.extension:prevision</t>
@@ -540,10 +702,6 @@
     <t>Encounter.modifierExtension</t>
   </si>
   <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
     <t>Extensions that cannot be ignored</t>
   </si>
   <si>
@@ -551,9 +709,6 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
     <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
@@ -567,7 +722,7 @@
 </t>
   </si>
   <si>
-    <t>ID DAU: identificador único del episodio en el establecimiento</t>
+    <t>ID DAU: sistema https://interoperabilidad.minsal.cl/fhir/sid/dau/[código DEIS]</t>
   </si>
   <si>
     <t>Identificador único del episodio de urgencia (ID DAU del CMBD). Debe ser el mismo en los mensajes de admisión, alta y abandono: es la llave con que la red correlaciona los eventos.</t>
@@ -588,35 +743,7 @@
     <t>Encounter.identifier.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>Encounter.identifier.extension</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>Encounter.identifier.use</t>
@@ -668,9 +795,6 @@
     <t>Allows users to make use of identifiers when the identifier system is not known.</t>
   </si>
   <si>
-    <t>extensible</t>
-  </si>
-  <si>
     <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
@@ -784,10 +908,10 @@
     <t>Encounter.status</t>
   </si>
   <si>
-    <t>in-progress (admitido) | finished (alta o abandono) | entered-in-error</t>
-  </si>
-  <si>
-    <t>Determina el estado del encuentro remoto conforme a los códigos definidos por el estándar</t>
+    <t>arrived (admitido) | finished (alta o abandono) | entered-in-error</t>
+  </si>
+  <si>
+    <t>Estado del episodio. Esta versión informa solo dos momentos: la admisión (arrived: el paciente llegó y está en la unidad) y el cierre (finished: alta o abandono). No se informan los estados intermedios (categorizado, en atención).</t>
   </si>
   <si>
     <t>Note that internal business rules will determine the appropriate transitions that may occur between statuses (and also classes).</t>
@@ -872,10 +996,6 @@
   </si>
   <si>
     <t>Encounter.class</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
   </si>
   <si>
     <t>Clase de encuentro: EMER (urgencia)</t>
@@ -956,9 +1076,6 @@
     <t>Since there are many ways to further classify encounters, this element is 0..*.</t>
   </si>
   <si>
-    <t>example</t>
-  </si>
-  <si>
     <t>https://hl7chile.cl/fhir/ig/clcore/ValueSet/VSTiposEncuentroCL</t>
   </si>
   <si>
@@ -1087,7 +1204,7 @@
     <t>Encounter.participant</t>
   </si>
   <si>
-    <t>Profesional que da el alta o atiende</t>
+    <t>ATND: médico tratante (period.start = inicio de la atención médica) | DIS: profesional que da el alta</t>
   </si>
   <si>
     <t>The list of people responsible for providing the service.</t>
@@ -1138,7 +1255,7 @@
     <t>Encounter.participant.period</t>
   </si>
   <si>
-    <t>Period of time during the encounter that the participant participated</t>
+    <t>Para ATND, period.start = fecha y hora de inicio de la atención médica</t>
   </si>
   <si>
     <t>The period of time that the specified participant participated in the encounter. These can overlap or be sub-sets of the overall encounter's period.</t>
@@ -1400,7 +1517,7 @@
     <t>Encounter.diagnosis</t>
   </si>
   <si>
-    <t>Hipótesis diagnóstica (AD) y diagnóstico de egreso (DD)</t>
+    <t>Diagnóstico de egreso (alta) o hipótesis diagnóstica (abandono)</t>
   </si>
   <si>
     <t>Diagnóstico relevante para este encuentro</t>
@@ -1425,11 +1542,11 @@
 discharge diagnosisindication</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7chile.cl/fhir/ig/clcore/StructureDefinition/CoreDiagnosticoCl)
+    <t xml:space="preserve">Reference(https://interoperabilidad.minsal.cl/fhir/ig/urgencia-eventos/StructureDefinition/diagnostico-urgencia)
 </t>
   </si>
   <si>
-    <t>Referencia a un Diagnóstico de urgencia incluido en el mismo mensaje</t>
+    <t>Diagnóstico de urgencia incluido en el mismo Bundle</t>
   </si>
   <si>
     <t>Reason the encounter takes place, as specified using information from another resource. For admissions, this is the admission diagnosis. The indication will typically be a Condition (with other resources referenced in the evidence.detail), or a Procedure.</t>
@@ -1447,7 +1564,7 @@
     <t>Encounter.diagnosis.use</t>
   </si>
   <si>
-    <t>AD (hipótesis de ingreso) | DD (diagnóstico de egreso)</t>
+    <t>DD: diagnóstico de egreso (obligatorio en el alta, no se usa en el abandono)</t>
   </si>
   <si>
     <t>Role that this diagnosis has within the encounter (e.g. admission, billing, discharge …).</t>
@@ -1669,7 +1786,11 @@
     <t>Encounter.hospitalization.destination</t>
   </si>
   <si>
-    <t>Establecimiento de destino (traslado o derivación)</t>
+    <t xml:space="preserve">Reference(https://interoperabilidad.minsal.cl/fhir/ig/nid/StructureDefinition/MINSALPrestadorOrganizacional)
+</t>
+  </si>
+  <si>
+    <t>Establecimiento de destino: obligatorio en hospitalización (01), traslado (02) y derivación (04)</t>
   </si>
   <si>
     <t>Location/organization to which the patient is discharged.</t>
@@ -1795,10 +1916,6 @@
   </si>
   <si>
     <t>Encounter.serviceProvider</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(https://interoperabilidad.minsal.cl/fhir/ig/nid/StructureDefinition/MINSALPrestadorOrganizacional)
-</t>
   </si>
   <si>
     <t>Establecimiento que realiza la atención</t>
@@ -2151,7 +2268,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN96"/>
+  <dimension ref="A1:AN104"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="39.6875" customWidth="true" bestFit="true"/>
@@ -2677,10 +2794,10 @@
         <v>80</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K5" t="s" s="2">
         <v>102</v>
@@ -2691,9 +2808,7 @@
       <c r="M5" t="s" s="2">
         <v>104</v>
       </c>
-      <c r="N5" t="s" s="2">
-        <v>105</v>
-      </c>
+      <c r="N5" s="2"/>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
         <v>80</v>
@@ -2742,25 +2857,25 @@
         <v>80</v>
       </c>
       <c r="AF5" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AG5" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH5" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI5" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ5" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK5" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL5" t="s" s="2">
         <v>106</v>
-      </c>
-      <c r="AG5" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH5" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI5" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ5" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK5" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL5" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AM5" t="s" s="2">
         <v>80</v>
@@ -2778,14 +2893,14 @@
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>80</v>
+        <v>108</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>80</v>
@@ -2797,16 +2912,16 @@
         <v>80</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2832,49 +2947,49 @@
         <v>80</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>112</v>
+        <v>80</v>
       </c>
       <c r="Y6" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z6" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA6" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB6" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="Z6" t="s" s="2">
+      <c r="AC6" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="AA6" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="AD6" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL6" t="s" s="2">
-        <v>80</v>
+        <v>106</v>
       </c>
       <c r="AM6" t="s" s="2">
         <v>80</v>
@@ -2885,14 +3000,14 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
@@ -2908,10 +3023,10 @@
         <v>80</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>118</v>
+        <v>90</v>
       </c>
       <c r="L7" t="s" s="2">
         <v>119</v>
@@ -2988,7 +3103,7 @@
         <v>80</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>123</v>
+        <v>80</v>
       </c>
       <c r="AM7" t="s" s="2">
         <v>80</v>
@@ -2999,21 +3114,21 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>125</v>
+        <v>80</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>80</v>
@@ -3022,19 +3137,19 @@
         <v>80</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="L8" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="M8" t="s" s="2">
         <v>126</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="N8" t="s" s="2">
         <v>127</v>
-      </c>
-      <c r="M8" t="s" s="2">
-        <v>128</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>129</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -3084,25 +3199,25 @@
         <v>80</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>131</v>
+        <v>80</v>
       </c>
       <c r="AM8" t="s" s="2">
         <v>80</v>
@@ -3113,10 +3228,10 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -3127,7 +3242,7 @@
         <v>78</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>80</v>
@@ -3136,18 +3251,20 @@
         <v>80</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="L9" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="M9" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="N9" t="s" s="2">
         <v>133</v>
       </c>
-      <c r="L9" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="M9" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="N9" s="2"/>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>80</v>
@@ -3184,29 +3301,31 @@
         <v>80</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="AC9" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="AC9" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="AD9" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>137</v>
+        <v>80</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>80</v>
@@ -3221,16 +3340,14 @@
         <v>80</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="C10" t="s" s="2">
-        <v>141</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
         <v>80</v>
       </c>
@@ -3239,27 +3356,29 @@
         <v>78</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H10" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I10" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J10" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="I10" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J10" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="K10" t="s" s="2">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="N10" s="2"/>
+        <v>138</v>
+      </c>
+      <c r="N10" t="s" s="2">
+        <v>139</v>
+      </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>80</v>
@@ -3308,7 +3427,7 @@
         <v>80</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -3317,10 +3436,10 @@
         <v>79</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>145</v>
+        <v>80</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>80</v>
@@ -3337,14 +3456,12 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="C11" t="s" s="2">
-        <v>147</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
         <v>80</v>
       </c>
@@ -3362,18 +3479,20 @@
         <v>80</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="N11" s="2"/>
+        <v>144</v>
+      </c>
+      <c r="N11" t="s" s="2">
+        <v>145</v>
+      </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>80</v>
@@ -3398,13 +3517,13 @@
         <v>80</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>80</v>
+        <v>146</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>80</v>
+        <v>147</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>80</v>
+        <v>148</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>80</v>
@@ -3422,7 +3541,7 @@
         <v>80</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -3431,10 +3550,10 @@
         <v>79</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>145</v>
+        <v>80</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>80</v>
@@ -3451,14 +3570,12 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="C12" t="s" s="2">
-        <v>152</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
         <v>80</v>
       </c>
@@ -3467,7 +3584,7 @@
         <v>78</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>80</v>
@@ -3476,18 +3593,20 @@
         <v>80</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="L12" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="M12" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="N12" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="L12" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="N12" s="2"/>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>80</v>
@@ -3512,13 +3631,13 @@
         <v>80</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>80</v>
+        <v>154</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>80</v>
+        <v>155</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>80</v>
+        <v>156</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>80</v>
@@ -3536,7 +3655,7 @@
         <v>80</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>138</v>
+        <v>157</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -3545,10 +3664,10 @@
         <v>79</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>145</v>
+        <v>80</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>80</v>
@@ -3565,14 +3684,12 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="C13" t="s" s="2">
-        <v>157</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
         <v>80</v>
       </c>
@@ -3587,13 +3704,13 @@
         <v>80</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>158</v>
+        <v>130</v>
       </c>
       <c r="L13" t="s" s="2">
         <v>159</v>
@@ -3601,7 +3718,9 @@
       <c r="M13" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="N13" s="2"/>
+      <c r="N13" t="s" s="2">
+        <v>161</v>
+      </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>80</v>
@@ -3650,19 +3769,19 @@
         <v>80</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>138</v>
+        <v>162</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>145</v>
+        <v>80</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>80</v>
@@ -3679,14 +3798,12 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="C14" t="s" s="2">
-        <v>162</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
         <v>80</v>
       </c>
@@ -3707,15 +3824,17 @@
         <v>80</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N14" s="2"/>
+        <v>166</v>
+      </c>
+      <c r="N14" t="s" s="2">
+        <v>167</v>
+      </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>80</v>
@@ -3740,13 +3859,13 @@
         <v>80</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>80</v>
+        <v>168</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>80</v>
+        <v>169</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>80</v>
@@ -3764,19 +3883,19 @@
         <v>80</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>138</v>
+        <v>171</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>145</v>
+        <v>80</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>80</v>
@@ -3793,46 +3912,44 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="J15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>133</v>
+        <v>174</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>171</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>80</v>
       </c>
@@ -3880,25 +3997,25 @@
         <v>80</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>131</v>
+        <v>179</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>80</v>
@@ -3907,43 +4024,45 @@
         <v>80</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>80</v>
+        <v>181</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G16" t="s" s="2">
         <v>79</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N16" s="2"/>
+        <v>184</v>
+      </c>
+      <c r="N16" t="s" s="2">
+        <v>185</v>
+      </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>80</v>
@@ -3992,7 +4111,7 @@
         <v>80</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -4004,27 +4123,27 @@
         <v>80</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>177</v>
+        <v>80</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>179</v>
+        <v>80</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>180</v>
+        <v>80</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4035,7 +4154,7 @@
         <v>78</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>80</v>
@@ -4047,13 +4166,13 @@
         <v>80</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>182</v>
+        <v>109</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -4092,37 +4211,35 @@
         <v>80</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="AC17" s="2"/>
       <c r="AD17" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>80</v>
+        <v>117</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>186</v>
+        <v>80</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>80</v>
@@ -4131,26 +4248,28 @@
         <v>80</v>
       </c>
     </row>
-    <row r="18" hidden="true">
+    <row r="18">
       <c r="A18" t="s" s="2">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="C18" s="2"/>
+        <v>188</v>
+      </c>
+      <c r="C18" t="s" s="2">
+        <v>193</v>
+      </c>
       <c r="D18" t="s" s="2">
-        <v>167</v>
+        <v>80</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>80</v>
@@ -4159,17 +4278,15 @@
         <v>80</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>133</v>
+        <v>194</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>170</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>80</v>
@@ -4206,16 +4323,16 @@
         <v>80</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>136</v>
+        <v>80</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>190</v>
+        <v>80</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>137</v>
+        <v>80</v>
       </c>
       <c r="AF18" t="s" s="2">
         <v>191</v>
@@ -4227,16 +4344,16 @@
         <v>79</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>80</v>
+        <v>197</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>186</v>
+        <v>80</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>80</v>
@@ -4245,14 +4362,16 @@
         <v>80</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="C19" s="2"/>
+        <v>188</v>
+      </c>
+      <c r="C19" t="s" s="2">
+        <v>199</v>
+      </c>
       <c r="D19" t="s" s="2">
         <v>80</v>
       </c>
@@ -4261,32 +4380,28 @@
         <v>78</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>108</v>
+        <v>200</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>196</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>80</v>
       </c>
@@ -4310,65 +4425,67 @@
         <v>80</v>
       </c>
       <c r="X19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF19" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AG19" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH19" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI19" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="Y19" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="Z19" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="AA19" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB19" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC19" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD19" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE19" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF19" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="AG19" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH19" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI19" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="AJ19" t="s" s="2">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>201</v>
+        <v>80</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>131</v>
+        <v>80</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="C20" s="2"/>
+        <v>188</v>
+      </c>
+      <c r="C20" t="s" s="2">
+        <v>204</v>
+      </c>
       <c r="D20" t="s" s="2">
         <v>80</v>
       </c>
@@ -4386,23 +4503,19 @@
         <v>80</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="O20" t="s" s="2">
         <v>207</v>
       </c>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>80</v>
       </c>
@@ -4426,99 +4539,97 @@
         <v>80</v>
       </c>
       <c r="X20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF20" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AG20" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH20" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI20" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AJ20" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="AK20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN20" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="21" hidden="true">
+      <c r="A21" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="Y20" t="s" s="2">
+      <c r="B21" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="C21" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="Z20" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="AA20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF20" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="AG20" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH20" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ20" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL20" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="AM20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN20" t="s" s="2">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="B21" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>102</v>
+        <v>210</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>217</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>80</v>
       </c>
@@ -4530,7 +4641,7 @@
         <v>80</v>
       </c>
       <c r="T21" t="s" s="2">
-        <v>218</v>
+        <v>80</v>
       </c>
       <c r="U21" t="s" s="2">
         <v>80</v>
@@ -4566,72 +4677,72 @@
         <v>80</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>219</v>
+        <v>191</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>80</v>
+        <v>197</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>220</v>
+        <v>80</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>221</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="C22" s="2"/>
+        <v>188</v>
+      </c>
+      <c r="C22" t="s" s="2">
+        <v>214</v>
+      </c>
       <c r="D22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>182</v>
+        <v>215</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>225</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="N22" s="2"/>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>80</v>
@@ -4644,7 +4755,7 @@
         <v>80</v>
       </c>
       <c r="T22" t="s" s="2">
-        <v>226</v>
+        <v>80</v>
       </c>
       <c r="U22" t="s" s="2">
         <v>80</v>
@@ -4680,71 +4791,75 @@
         <v>80</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>227</v>
+        <v>191</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>80</v>
+        <v>197</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>228</v>
+        <v>80</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>229</v>
+        <v>80</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>230</v>
+        <v>218</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>230</v>
+        <v>218</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>80</v>
+        <v>108</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>231</v>
+        <v>109</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>232</v>
+        <v>219</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="N23" s="2"/>
-      <c r="O23" s="2"/>
+        <v>220</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="O23" t="s" s="2">
+        <v>221</v>
+      </c>
       <c r="P23" t="s" s="2">
         <v>80</v>
       </c>
@@ -4792,39 +4907,39 @@
         <v>80</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>235</v>
+        <v>187</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>236</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
-        <v>237</v>
+        <v>223</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>237</v>
+        <v>223</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4832,13 +4947,13 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>80</v>
@@ -4847,17 +4962,15 @@
         <v>89</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>238</v>
+        <v>224</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>239</v>
+        <v>225</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>241</v>
-      </c>
+        <v>226</v>
+      </c>
+      <c r="N24" s="2"/>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>80</v>
@@ -4906,13 +5019,13 @@
         <v>80</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>242</v>
+        <v>223</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>80</v>
@@ -4921,24 +5034,24 @@
         <v>100</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>80</v>
+        <v>227</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>80</v>
+        <v>229</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>244</v>
+        <v>230</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4946,32 +5059,30 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>246</v>
+        <v>103</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>248</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="N25" s="2"/>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>80</v>
@@ -4996,11 +5107,13 @@
         <v>80</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="Y25" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="Y25" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="Z25" t="s" s="2">
-        <v>249</v>
+        <v>80</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>80</v>
@@ -5018,10 +5131,10 @@
         <v>80</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>245</v>
+        <v>105</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH25" t="s" s="2">
         <v>88</v>
@@ -5030,31 +5143,31 @@
         <v>80</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>250</v>
+        <v>80</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>251</v>
+        <v>106</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>252</v>
+        <v>80</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>253</v>
+        <v>80</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>254</v>
+        <v>232</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>254</v>
+        <v>232</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>80</v>
+        <v>108</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -5073,16 +5186,16 @@
         <v>80</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>255</v>
+        <v>109</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>256</v>
+        <v>110</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>257</v>
+        <v>111</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>258</v>
+        <v>112</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -5120,19 +5233,19 @@
         <v>80</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>254</v>
+        <v>116</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -5144,13 +5257,13 @@
         <v>80</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>186</v>
+        <v>106</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>80</v>
@@ -5161,10 +5274,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>259</v>
+        <v>233</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>259</v>
+        <v>233</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5181,22 +5294,26 @@
         <v>80</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>183</v>
+        <v>234</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="N27" s="2"/>
-      <c r="O27" s="2"/>
+        <v>235</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="O27" t="s" s="2">
+        <v>237</v>
+      </c>
       <c r="P27" t="s" s="2">
         <v>80</v>
       </c>
@@ -5220,13 +5337,13 @@
         <v>80</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>80</v>
+        <v>238</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>80</v>
+        <v>239</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>80</v>
+        <v>240</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>80</v>
@@ -5244,7 +5361,7 @@
         <v>80</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>185</v>
+        <v>241</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -5256,38 +5373,38 @@
         <v>80</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>186</v>
+        <v>242</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>80</v>
+        <v>187</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>260</v>
+        <v>243</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>260</v>
+        <v>243</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>167</v>
+        <v>80</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>80</v>
@@ -5296,21 +5413,23 @@
         <v>80</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>133</v>
+        <v>244</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>188</v>
+        <v>245</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>189</v>
+        <v>246</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="O28" s="2"/>
+        <v>247</v>
+      </c>
+      <c r="O28" t="s" s="2">
+        <v>248</v>
+      </c>
       <c r="P28" t="s" s="2">
         <v>80</v>
       </c>
@@ -5334,13 +5453,13 @@
         <v>80</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>80</v>
+        <v>146</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>80</v>
+        <v>249</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>80</v>
+        <v>250</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>80</v>
@@ -5358,74 +5477,74 @@
         <v>80</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>191</v>
+        <v>251</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>186</v>
+        <v>242</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>80</v>
+        <v>252</v>
       </c>
     </row>
-    <row r="29" hidden="true">
+    <row r="29">
       <c r="A29" t="s" s="2">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>262</v>
+        <v>80</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="J29" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>170</v>
+        <v>256</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>171</v>
+        <v>257</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>80</v>
@@ -5438,7 +5557,7 @@
         <v>80</v>
       </c>
       <c r="T29" t="s" s="2">
-        <v>80</v>
+        <v>258</v>
       </c>
       <c r="U29" t="s" s="2">
         <v>80</v>
@@ -5474,39 +5593,39 @@
         <v>80</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>131</v>
+        <v>260</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>80</v>
+        <v>261</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5520,24 +5639,26 @@
         <v>88</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="N30" s="2"/>
+        <v>264</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>265</v>
+      </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>80</v>
@@ -5550,7 +5671,7 @@
         <v>80</v>
       </c>
       <c r="T30" t="s" s="2">
-        <v>80</v>
+        <v>266</v>
       </c>
       <c r="U30" t="s" s="2">
         <v>80</v>
@@ -5562,13 +5683,13 @@
         <v>80</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>197</v>
+        <v>80</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>269</v>
+        <v>80</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>270</v>
+        <v>80</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>80</v>
@@ -5586,10 +5707,10 @@
         <v>80</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH30" t="s" s="2">
         <v>88</v>
@@ -5604,21 +5725,21 @@
         <v>80</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>186</v>
+        <v>268</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>80</v>
+        <v>269</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5626,7 +5747,7 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>88</v>
@@ -5638,10 +5759,10 @@
         <v>80</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>231</v>
+        <v>271</v>
       </c>
       <c r="L31" t="s" s="2">
         <v>272</v>
@@ -5698,10 +5819,10 @@
         <v>80</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH31" t="s" s="2">
         <v>88</v>
@@ -5716,21 +5837,21 @@
         <v>80</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>186</v>
+        <v>275</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>80</v>
+        <v>276</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5738,13 +5859,13 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>80</v>
@@ -5753,15 +5874,17 @@
         <v>89</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>280</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>281</v>
+      </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>80</v>
@@ -5771,7 +5894,7 @@
         <v>80</v>
       </c>
       <c r="S32" t="s" s="2">
-        <v>278</v>
+        <v>80</v>
       </c>
       <c r="T32" t="s" s="2">
         <v>80</v>
@@ -5786,11 +5909,13 @@
         <v>80</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="Y32" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="Y32" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="Z32" t="s" s="2">
-        <v>279</v>
+        <v>80</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>80</v>
@@ -5808,10 +5933,10 @@
         <v>80</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH32" t="s" s="2">
         <v>88</v>
@@ -5826,21 +5951,21 @@
         <v>80</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>281</v>
+        <v>80</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5848,30 +5973,32 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>255</v>
+        <v>164</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="N33" s="2"/>
+        <v>287</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>288</v>
+      </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>80</v>
@@ -5896,13 +6023,11 @@
         <v>80</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y33" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>238</v>
+      </c>
+      <c r="Y33" s="2"/>
       <c r="Z33" t="s" s="2">
-        <v>80</v>
+        <v>289</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>80</v>
@@ -5920,13 +6045,13 @@
         <v>80</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>80</v>
@@ -5935,24 +6060,24 @@
         <v>100</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>80</v>
+        <v>290</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>186</v>
+        <v>291</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>80</v>
+        <v>292</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>80</v>
+        <v>293</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5963,7 +6088,7 @@
         <v>78</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>80</v>
@@ -5975,15 +6100,17 @@
         <v>80</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>182</v>
+        <v>295</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>183</v>
+        <v>296</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="N34" s="2"/>
+        <v>297</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>298</v>
+      </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>80</v>
@@ -6032,25 +6159,25 @@
         <v>80</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>185</v>
+        <v>294</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>186</v>
+        <v>106</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>80</v>
@@ -6061,21 +6188,21 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>287</v>
+        <v>299</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>287</v>
+        <v>299</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>167</v>
+        <v>80</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>80</v>
@@ -6087,17 +6214,15 @@
         <v>80</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>133</v>
+        <v>102</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>188</v>
+        <v>103</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>170</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>80</v>
@@ -6146,25 +6271,25 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>191</v>
+        <v>105</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>139</v>
+        <v>80</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>186</v>
+        <v>106</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>80</v>
@@ -6175,14 +6300,14 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>262</v>
+        <v>108</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -6195,26 +6320,24 @@
         <v>80</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>133</v>
+        <v>109</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>263</v>
+        <v>110</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>264</v>
+        <v>111</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>171</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>80</v>
       </c>
@@ -6262,7 +6385,7 @@
         <v>80</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>265</v>
+        <v>116</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -6274,13 +6397,13 @@
         <v>80</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>131</v>
+        <v>106</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>80</v>
@@ -6291,42 +6414,46 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>80</v>
+        <v>302</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>275</v>
+        <v>109</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>290</v>
+        <v>303</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="N37" s="2"/>
-      <c r="O37" s="2"/>
+        <v>304</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="O37" t="s" s="2">
+        <v>221</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>80</v>
       </c>
@@ -6350,13 +6477,13 @@
         <v>80</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>208</v>
+        <v>80</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>292</v>
+        <v>80</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>293</v>
+        <v>80</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>80</v>
@@ -6374,25 +6501,25 @@
         <v>80</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>80</v>
@@ -6403,10 +6530,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>294</v>
+        <v>306</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>294</v>
+        <v>306</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6429,13 +6556,13 @@
         <v>80</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>231</v>
+        <v>164</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>295</v>
+        <v>307</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6462,13 +6589,13 @@
         <v>80</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>80</v>
+        <v>238</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>80</v>
+        <v>309</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>80</v>
+        <v>310</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>80</v>
@@ -6486,7 +6613,7 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>294</v>
+        <v>306</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>88</v>
@@ -6504,7 +6631,7 @@
         <v>80</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>186</v>
+        <v>106</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>80</v>
@@ -6513,12 +6640,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>297</v>
+        <v>311</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>297</v>
+        <v>311</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6526,32 +6653,30 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>203</v>
+        <v>271</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>298</v>
+        <v>312</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>300</v>
-      </c>
+        <v>313</v>
+      </c>
+      <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>80</v>
@@ -6576,11 +6701,13 @@
         <v>80</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="Y39" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="Y39" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="Z39" t="s" s="2">
-        <v>302</v>
+        <v>80</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>80</v>
@@ -6598,13 +6725,13 @@
         <v>80</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>297</v>
+        <v>311</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>80</v>
@@ -6613,24 +6740,24 @@
         <v>100</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>303</v>
+        <v>80</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>304</v>
+        <v>106</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>281</v>
+        <v>80</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>305</v>
+        <v>80</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6638,7 +6765,7 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>88</v>
@@ -6653,13 +6780,13 @@
         <v>89</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>203</v>
+        <v>142</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6671,7 +6798,7 @@
         <v>80</v>
       </c>
       <c r="S40" t="s" s="2">
-        <v>80</v>
+        <v>317</v>
       </c>
       <c r="T40" t="s" s="2">
         <v>80</v>
@@ -6686,11 +6813,11 @@
         <v>80</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>197</v>
+        <v>146</v>
       </c>
       <c r="Y40" s="2"/>
       <c r="Z40" t="s" s="2">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>80</v>
@@ -6708,10 +6835,10 @@
         <v>80</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH40" t="s" s="2">
         <v>88</v>
@@ -6723,24 +6850,24 @@
         <v>100</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>303</v>
+        <v>80</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>186</v>
+        <v>319</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>80</v>
+        <v>320</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>310</v>
+        <v>321</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6751,7 +6878,7 @@
         <v>78</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>80</v>
@@ -6763,13 +6890,13 @@
         <v>80</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>203</v>
+        <v>295</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>312</v>
+        <v>323</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>313</v>
+        <v>324</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6796,13 +6923,13 @@
         <v>80</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>301</v>
+        <v>80</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>313</v>
+        <v>80</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>314</v>
+        <v>80</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>80</v>
@@ -6820,13 +6947,13 @@
         <v>80</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>80</v>
@@ -6838,54 +6965,52 @@
         <v>80</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>315</v>
+        <v>106</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>316</v>
+        <v>80</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>317</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>319</v>
+        <v>80</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G42" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>320</v>
+        <v>102</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>321</v>
+        <v>103</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>323</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>80</v>
@@ -6934,7 +7059,7 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>318</v>
+        <v>105</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6946,31 +7071,31 @@
         <v>80</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>324</v>
+        <v>80</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>325</v>
+        <v>106</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>326</v>
+        <v>80</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>327</v>
+        <v>80</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>80</v>
+        <v>108</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6986,18 +7111,20 @@
         <v>80</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>329</v>
+        <v>109</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>330</v>
+        <v>110</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="N43" s="2"/>
+        <v>111</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>112</v>
+      </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>80</v>
@@ -7046,7 +7173,7 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>328</v>
+        <v>116</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -7058,31 +7185,31 @@
         <v>80</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>332</v>
+        <v>80</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>186</v>
+        <v>106</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>333</v>
+        <v>80</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>334</v>
+        <v>80</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>336</v>
+        <v>302</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7095,22 +7222,26 @@
         <v>80</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>337</v>
+        <v>109</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>338</v>
+        <v>303</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="N44" s="2"/>
-      <c r="O44" s="2"/>
+        <v>304</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>221</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>80</v>
       </c>
@@ -7158,7 +7289,7 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>335</v>
+        <v>305</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -7170,13 +7301,13 @@
         <v>80</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>340</v>
+        <v>80</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>341</v>
+        <v>187</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>80</v>
@@ -7185,12 +7316,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>342</v>
+        <v>328</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>342</v>
+        <v>328</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7198,28 +7329,28 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>255</v>
+        <v>142</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>343</v>
+        <v>329</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>344</v>
+        <v>330</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7246,13 +7377,13 @@
         <v>80</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>80</v>
+        <v>146</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>80</v>
+        <v>331</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>80</v>
+        <v>332</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>80</v>
@@ -7270,13 +7401,13 @@
         <v>80</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>342</v>
+        <v>328</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>80</v>
@@ -7285,24 +7416,24 @@
         <v>100</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>345</v>
+        <v>80</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>346</v>
+        <v>106</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>347</v>
+        <v>80</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>348</v>
+        <v>333</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>348</v>
+        <v>333</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7310,7 +7441,7 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>88</v>
@@ -7325,13 +7456,13 @@
         <v>80</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>182</v>
+        <v>271</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>183</v>
+        <v>334</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>184</v>
+        <v>335</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7382,10 +7513,10 @@
         <v>80</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>185</v>
+        <v>333</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH46" t="s" s="2">
         <v>88</v>
@@ -7394,13 +7525,13 @@
         <v>80</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>186</v>
+        <v>106</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>80</v>
@@ -7409,16 +7540,16 @@
         <v>80</v>
       </c>
     </row>
-    <row r="47" hidden="true">
+    <row r="47">
       <c r="A47" t="s" s="2">
-        <v>349</v>
+        <v>336</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>349</v>
+        <v>336</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>167</v>
+        <v>80</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7428,25 +7559,25 @@
         <v>79</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>133</v>
+        <v>244</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>188</v>
+        <v>337</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>189</v>
+        <v>338</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>170</v>
+        <v>339</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7472,13 +7603,11 @@
         <v>80</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y47" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="Y47" s="2"/>
       <c r="Z47" t="s" s="2">
-        <v>80</v>
+        <v>340</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>80</v>
@@ -7496,7 +7625,7 @@
         <v>80</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>191</v>
+        <v>336</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7508,63 +7637,59 @@
         <v>80</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>80</v>
+        <v>341</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>186</v>
+        <v>342</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>80</v>
+        <v>320</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>80</v>
+        <v>343</v>
       </c>
     </row>
-    <row r="48" hidden="true">
+    <row r="48">
       <c r="A48" t="s" s="2">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>262</v>
+        <v>80</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="J48" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>133</v>
+        <v>244</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>263</v>
+        <v>345</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>171</v>
-      </c>
+        <v>346</v>
+      </c>
+      <c r="N48" s="2"/>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>80</v>
       </c>
@@ -7588,13 +7713,11 @@
         <v>80</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y48" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>238</v>
+      </c>
+      <c r="Y48" s="2"/>
       <c r="Z48" t="s" s="2">
-        <v>80</v>
+        <v>347</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>80</v>
@@ -7612,39 +7735,39 @@
         <v>80</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>265</v>
+        <v>344</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>80</v>
+        <v>341</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>131</v>
+        <v>106</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>80</v>
+        <v>348</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7655,29 +7778,27 @@
         <v>78</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>203</v>
+        <v>244</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>354</v>
-      </c>
+        <v>351</v>
+      </c>
+      <c r="N49" s="2"/>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>80</v>
@@ -7702,11 +7823,13 @@
         <v>80</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="Y49" s="2"/>
+        <v>154</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>351</v>
+      </c>
       <c r="Z49" t="s" s="2">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>80</v>
@@ -7724,13 +7847,13 @@
         <v>80</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>80</v>
@@ -7739,55 +7862,57 @@
         <v>100</v>
       </c>
       <c r="AK49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="AN49" t="s" s="2">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="AL49" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="AM49" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="50" hidden="true">
-      <c r="A50" t="s" s="2">
-        <v>359</v>
-      </c>
       <c r="B50" t="s" s="2">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>80</v>
+        <v>357</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G50" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>231</v>
+        <v>358</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>80</v>
@@ -7836,7 +7961,7 @@
         <v>80</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7851,24 +7976,24 @@
         <v>100</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>80</v>
+        <v>362</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>80</v>
+        <v>364</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7876,13 +8001,13 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>80</v>
@@ -7891,13 +8016,13 @@
         <v>89</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7948,13 +8073,13 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>80</v>
@@ -7963,53 +8088,53 @@
         <v>100</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>369</v>
+        <v>106</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>80</v>
+        <v>374</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8060,7 +8185,7 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -8075,24 +8200,24 @@
         <v>100</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>340</v>
+        <v>378</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>377</v>
+        <v>80</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8100,10 +8225,10 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>89</v>
@@ -8112,20 +8237,18 @@
         <v>80</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>231</v>
+        <v>295</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>381</v>
-      </c>
+        <v>382</v>
+      </c>
+      <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>80</v>
@@ -8174,13 +8297,13 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>80</v>
@@ -8189,13 +8312,13 @@
         <v>100</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>384</v>
+        <v>80</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>385</v>
@@ -8229,13 +8352,13 @@
         <v>80</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>182</v>
+        <v>102</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>183</v>
+        <v>103</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>184</v>
+        <v>104</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8286,7 +8409,7 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>185</v>
+        <v>105</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8304,7 +8427,7 @@
         <v>80</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>186</v>
+        <v>106</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>80</v>
@@ -8322,7 +8445,7 @@
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>167</v>
+        <v>108</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8341,16 +8464,16 @@
         <v>80</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>133</v>
+        <v>109</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>188</v>
+        <v>110</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>189</v>
+        <v>111</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>170</v>
+        <v>112</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8388,19 +8511,19 @@
         <v>80</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>136</v>
+        <v>80</v>
       </c>
       <c r="AC55" t="s" s="2">
-        <v>190</v>
+        <v>80</v>
       </c>
       <c r="AD55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>137</v>
+        <v>80</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>191</v>
+        <v>116</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8412,13 +8535,13 @@
         <v>80</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>186</v>
+        <v>106</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>80</v>
@@ -8427,7 +8550,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
         <v>388</v>
       </c>
@@ -8436,37 +8559,39 @@
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>80</v>
+        <v>302</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I56" t="s" s="2">
         <v>89</v>
-      </c>
-      <c r="I56" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="J56" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>389</v>
+        <v>109</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>390</v>
+        <v>303</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>391</v>
+        <v>304</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="O56" s="2"/>
+        <v>112</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>221</v>
+      </c>
       <c r="P56" t="s" s="2">
         <v>80</v>
       </c>
@@ -8514,39 +8639,39 @@
         <v>80</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>393</v>
+        <v>305</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>394</v>
+        <v>80</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>395</v>
+        <v>187</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>396</v>
+        <v>80</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8557,7 +8682,7 @@
         <v>78</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>89</v>
@@ -8569,24 +8694,22 @@
         <v>89</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>389</v>
+        <v>244</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="Q57" t="s" s="2">
-        <v>401</v>
-      </c>
+      <c r="Q57" s="2"/>
       <c r="R57" t="s" s="2">
         <v>80</v>
       </c>
@@ -8606,13 +8729,11 @@
         <v>80</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y57" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="Y57" s="2"/>
       <c r="Z57" t="s" s="2">
-        <v>80</v>
+        <v>393</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>80</v>
@@ -8630,39 +8751,39 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>402</v>
+        <v>389</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>394</v>
+        <v>80</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>80</v>
+        <v>394</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>404</v>
+        <v>396</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8685,17 +8806,15 @@
         <v>80</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>406</v>
+        <v>271</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>407</v>
+        <v>398</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>408</v>
-      </c>
+        <v>399</v>
+      </c>
+      <c r="N58" s="2"/>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>80</v>
@@ -8744,7 +8863,7 @@
         <v>80</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8759,32 +8878,32 @@
         <v>100</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>382</v>
+        <v>80</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>409</v>
+        <v>400</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>410</v>
+        <v>401</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>411</v>
+        <v>402</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>411</v>
+        <v>402</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>412</v>
+        <v>80</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G59" t="s" s="2">
         <v>88</v>
@@ -8799,17 +8918,15 @@
         <v>89</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>203</v>
+        <v>403</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>413</v>
+        <v>404</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>415</v>
-      </c>
+        <v>405</v>
+      </c>
+      <c r="N59" s="2"/>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>80</v>
@@ -8834,13 +8951,13 @@
         <v>80</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>112</v>
+        <v>80</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>416</v>
+        <v>80</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>417</v>
+        <v>80</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>80</v>
@@ -8858,13 +8975,13 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>411</v>
+        <v>402</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>80</v>
@@ -8873,24 +8990,24 @@
         <v>100</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>418</v>
+        <v>406</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>419</v>
+        <v>407</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>420</v>
+        <v>408</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>421</v>
+        <v>409</v>
       </c>
     </row>
-    <row r="60" hidden="true">
+    <row r="60">
       <c r="A60" t="s" s="2">
-        <v>422</v>
+        <v>410</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>422</v>
+        <v>410</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8904,22 +9021,22 @@
         <v>88</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>182</v>
+        <v>411</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>183</v>
+        <v>412</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>184</v>
+        <v>413</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8970,53 +9087,53 @@
         <v>80</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>185</v>
+        <v>410</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>80</v>
+        <v>378</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>186</v>
+        <v>414</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>80</v>
+        <v>415</v>
       </c>
     </row>
-    <row r="61" hidden="true">
+    <row r="61">
       <c r="A61" t="s" s="2">
-        <v>423</v>
+        <v>416</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>423</v>
+        <v>416</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>167</v>
+        <v>80</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>80</v>
@@ -9025,16 +9142,16 @@
         <v>80</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>133</v>
+        <v>271</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>188</v>
+        <v>417</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>189</v>
+        <v>418</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>170</v>
+        <v>419</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9072,43 +9189,43 @@
         <v>80</v>
       </c>
       <c r="AB61" t="s" s="2">
-        <v>136</v>
+        <v>80</v>
       </c>
       <c r="AC61" t="s" s="2">
-        <v>190</v>
+        <v>80</v>
       </c>
       <c r="AD61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>137</v>
+        <v>80</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>191</v>
+        <v>416</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>80</v>
+        <v>420</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>186</v>
+        <v>421</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>80</v>
+        <v>422</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>80</v>
+        <v>423</v>
       </c>
     </row>
     <row r="62" hidden="true">
@@ -9127,7 +9244,7 @@
         <v>78</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>80</v>
@@ -9136,23 +9253,19 @@
         <v>80</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>275</v>
+        <v>102</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>425</v>
+        <v>103</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>428</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="N62" s="2"/>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>80</v>
       </c>
@@ -9200,75 +9313,73 @@
         <v>80</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>429</v>
+        <v>105</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>430</v>
+        <v>106</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>431</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>432</v>
+        <v>425</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>432</v>
+        <v>425</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>80</v>
+        <v>108</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>182</v>
+        <v>109</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>433</v>
+        <v>110</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>434</v>
+        <v>111</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>436</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>80</v>
       </c>
@@ -9304,65 +9415,65 @@
         <v>80</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="AC63" t="s" s="2">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="AD63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>437</v>
+        <v>116</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>438</v>
+        <v>106</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>439</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="64" hidden="true">
+    <row r="64">
       <c r="A64" t="s" s="2">
-        <v>440</v>
+        <v>426</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>440</v>
+        <v>426</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>412</v>
+        <v>80</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>80</v>
@@ -9371,16 +9482,16 @@
         <v>89</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>441</v>
+        <v>427</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>442</v>
+        <v>428</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>443</v>
+        <v>429</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>415</v>
+        <v>430</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9430,39 +9541,39 @@
         <v>80</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>440</v>
+        <v>431</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>80</v>
+        <v>432</v>
       </c>
       <c r="AJ64" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>418</v>
+        <v>80</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>419</v>
+        <v>433</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>420</v>
+        <v>80</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>421</v>
+        <v>434</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>444</v>
+        <v>435</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>444</v>
+        <v>435</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9473,7 +9584,7 @@
         <v>78</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>89</v>
@@ -9485,20 +9596,24 @@
         <v>89</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>255</v>
+        <v>427</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>445</v>
+        <v>436</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="N65" s="2"/>
+        <v>437</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>438</v>
+      </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="Q65" s="2"/>
+      <c r="Q65" t="s" s="2">
+        <v>439</v>
+      </c>
       <c r="R65" t="s" s="2">
         <v>80</v>
       </c>
@@ -9542,16 +9657,16 @@
         <v>80</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>80</v>
+        <v>432</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>100</v>
@@ -9560,21 +9675,21 @@
         <v>80</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>80</v>
+        <v>442</v>
       </c>
     </row>
-    <row r="66" hidden="true">
+    <row r="66">
       <c r="A66" t="s" s="2">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9588,7 +9703,7 @@
         <v>88</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I66" t="s" s="2">
         <v>80</v>
@@ -9597,15 +9712,17 @@
         <v>80</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>182</v>
+        <v>444</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>183</v>
+        <v>445</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="N66" s="2"/>
+        <v>445</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>446</v>
+      </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>80</v>
@@ -9654,7 +9771,7 @@
         <v>80</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>185</v>
+        <v>443</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -9666,22 +9783,22 @@
         <v>80</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>80</v>
+        <v>420</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>186</v>
+        <v>447</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>80</v>
+        <v>448</v>
       </c>
     </row>
-    <row r="67" hidden="true">
+    <row r="67">
       <c r="A67" t="s" s="2">
         <v>449</v>
       </c>
@@ -9690,35 +9807,35 @@
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>167</v>
+        <v>450</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>133</v>
+        <v>244</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>188</v>
+        <v>451</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>189</v>
+        <v>452</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>170</v>
+        <v>453</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9744,13 +9861,13 @@
         <v>80</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>80</v>
+        <v>168</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>80</v>
+        <v>454</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>80</v>
+        <v>455</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>80</v>
@@ -9768,7 +9885,7 @@
         <v>80</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>191</v>
+        <v>449</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -9780,63 +9897,59 @@
         <v>80</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>80</v>
+        <v>456</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>186</v>
+        <v>457</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>80</v>
+        <v>458</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>80</v>
+        <v>459</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>262</v>
+        <v>80</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I68" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>133</v>
+        <v>102</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>263</v>
+        <v>103</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>171</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="N68" s="2"/>
+      <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>80</v>
       </c>
@@ -9884,25 +9997,25 @@
         <v>80</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>265</v>
+        <v>105</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>139</v>
+        <v>80</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>131</v>
+        <v>106</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>80</v>
@@ -9913,21 +10026,21 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>451</v>
+        <v>461</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>451</v>
+        <v>461</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>452</v>
+        <v>108</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>80</v>
@@ -9936,19 +10049,19 @@
         <v>80</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>453</v>
+        <v>109</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>454</v>
+        <v>110</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>455</v>
+        <v>111</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>415</v>
+        <v>112</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -9986,51 +10099,51 @@
         <v>80</v>
       </c>
       <c r="AB69" t="s" s="2">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="AC69" t="s" s="2">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="AD69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE69" t="s" s="2">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>451</v>
+        <v>116</v>
       </c>
       <c r="AG69" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>456</v>
+        <v>80</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>457</v>
+        <v>106</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>420</v>
+        <v>80</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>458</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10038,31 +10151,35 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J70" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="I70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J70" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="K70" t="s" s="2">
-        <v>203</v>
+        <v>142</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="N70" s="2"/>
-      <c r="O70" s="2"/>
+        <v>464</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="O70" t="s" s="2">
+        <v>466</v>
+      </c>
       <c r="P70" t="s" s="2">
         <v>80</v>
       </c>
@@ -10086,11 +10203,13 @@
         <v>80</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="Y70" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="Z70" t="s" s="2">
-        <v>462</v>
+        <v>80</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>80</v>
@@ -10108,13 +10227,13 @@
         <v>80</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>80</v>
@@ -10126,21 +10245,21 @@
         <v>80</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>186</v>
+        <v>468</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>80</v>
+        <v>469</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>463</v>
+        <v>470</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>463</v>
+        <v>470</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10148,7 +10267,7 @@
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G71" t="s" s="2">
         <v>88</v>
@@ -10160,19 +10279,23 @@
         <v>80</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>464</v>
+        <v>102</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="N71" s="2"/>
-      <c r="O71" s="2"/>
+        <v>472</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="O71" t="s" s="2">
+        <v>474</v>
+      </c>
       <c r="P71" t="s" s="2">
         <v>80</v>
       </c>
@@ -10220,7 +10343,7 @@
         <v>80</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>463</v>
+        <v>475</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -10238,25 +10361,25 @@
         <v>80</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>467</v>
+        <v>476</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>80</v>
+        <v>477</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>468</v>
+        <v>478</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>468</v>
+        <v>478</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>80</v>
+        <v>450</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -10272,19 +10395,19 @@
         <v>80</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>469</v>
+        <v>479</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>470</v>
+        <v>480</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>471</v>
+        <v>481</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>472</v>
+        <v>453</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10334,7 +10457,7 @@
         <v>80</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>468</v>
+        <v>478</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -10349,24 +10472,24 @@
         <v>100</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>80</v>
+        <v>456</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>473</v>
+        <v>457</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>80</v>
+        <v>458</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>80</v>
+        <v>459</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>474</v>
+        <v>482</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>474</v>
+        <v>482</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10377,7 +10500,7 @@
         <v>78</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>89</v>
@@ -10386,20 +10509,18 @@
         <v>80</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>255</v>
+        <v>295</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>475</v>
+        <v>483</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>477</v>
-      </c>
+        <v>484</v>
+      </c>
+      <c r="N73" s="2"/>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>80</v>
@@ -10448,13 +10569,13 @@
         <v>80</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>474</v>
+        <v>482</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>80</v>
@@ -10466,7 +10587,7 @@
         <v>80</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>478</v>
+        <v>485</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>80</v>
@@ -10477,10 +10598,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>479</v>
+        <v>486</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>479</v>
+        <v>486</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10503,13 +10624,13 @@
         <v>80</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>182</v>
+        <v>102</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>183</v>
+        <v>103</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>184</v>
+        <v>104</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10560,7 +10681,7 @@
         <v>80</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>185</v>
+        <v>105</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -10578,7 +10699,7 @@
         <v>80</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>186</v>
+        <v>106</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>80</v>
@@ -10589,14 +10710,14 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>480</v>
+        <v>487</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>480</v>
+        <v>487</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>80</v>
+        <v>108</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -10615,15 +10736,17 @@
         <v>80</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>133</v>
+        <v>109</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>481</v>
+        <v>110</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="N75" s="2"/>
+        <v>111</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>112</v>
+      </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>80</v>
@@ -10660,17 +10783,19 @@
         <v>80</v>
       </c>
       <c r="AB75" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="AC75" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="AD75" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE75" t="s" s="2">
-        <v>137</v>
+        <v>80</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>191</v>
+        <v>116</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -10682,13 +10807,13 @@
         <v>80</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>80</v>
+        <v>106</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>80</v>
@@ -10697,46 +10822,48 @@
         <v>80</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="C76" t="s" s="2">
-        <v>483</v>
-      </c>
+        <v>488</v>
+      </c>
+      <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>80</v>
+        <v>302</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I76" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="I76" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="J76" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>484</v>
+        <v>109</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>481</v>
+        <v>303</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="N76" s="2"/>
-      <c r="O76" s="2"/>
+        <v>304</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="O76" t="s" s="2">
+        <v>221</v>
+      </c>
       <c r="P76" t="s" s="2">
         <v>80</v>
       </c>
@@ -10784,7 +10911,7 @@
         <v>80</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>191</v>
+        <v>305</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
@@ -10793,16 +10920,16 @@
         <v>79</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>145</v>
+        <v>80</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>80</v>
+        <v>187</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>80</v>
@@ -10813,46 +10940,44 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>262</v>
+        <v>490</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I77" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="J77" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>133</v>
+        <v>491</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>263</v>
+        <v>492</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>264</v>
+        <v>493</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>171</v>
-      </c>
+        <v>453</v>
+      </c>
+      <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>80</v>
       </c>
@@ -10900,39 +11025,39 @@
         <v>80</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>265</v>
+        <v>489</v>
       </c>
       <c r="AG77" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>80</v>
+        <v>494</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>131</v>
+        <v>495</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>80</v>
+        <v>458</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>80</v>
+        <v>496</v>
       </c>
     </row>
-    <row r="78" hidden="true">
+    <row r="78">
       <c r="A78" t="s" s="2">
-        <v>487</v>
+        <v>497</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>487</v>
+        <v>497</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10946,7 +11071,7 @@
         <v>88</v>
       </c>
       <c r="H78" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I78" t="s" s="2">
         <v>80</v>
@@ -10955,13 +11080,13 @@
         <v>80</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>174</v>
+        <v>244</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>488</v>
+        <v>498</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>489</v>
+        <v>499</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -10988,13 +11113,11 @@
         <v>80</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y78" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>238</v>
+      </c>
+      <c r="Y78" s="2"/>
       <c r="Z78" t="s" s="2">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>80</v>
@@ -11012,7 +11135,7 @@
         <v>80</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>487</v>
+        <v>497</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -11030,21 +11153,21 @@
         <v>80</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>178</v>
+        <v>106</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>490</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="79" hidden="true">
+    <row r="79">
       <c r="A79" t="s" s="2">
-        <v>491</v>
+        <v>501</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>491</v>
+        <v>501</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11058,7 +11181,7 @@
         <v>88</v>
       </c>
       <c r="H79" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I79" t="s" s="2">
         <v>80</v>
@@ -11067,13 +11190,13 @@
         <v>80</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>492</v>
+        <v>502</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>493</v>
+        <v>503</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>494</v>
+        <v>504</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11124,7 +11247,7 @@
         <v>80</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>491</v>
+        <v>501</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -11142,7 +11265,7 @@
         <v>80</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>495</v>
+        <v>505</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>80</v>
@@ -11151,12 +11274,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>496</v>
+        <v>506</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>496</v>
+        <v>506</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11167,10 +11290,10 @@
         <v>78</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H80" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="I80" t="s" s="2">
         <v>80</v>
@@ -11179,15 +11302,17 @@
         <v>80</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>203</v>
+        <v>507</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>497</v>
+        <v>508</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="N80" s="2"/>
+        <v>509</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>510</v>
+      </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>80</v>
@@ -11212,11 +11337,13 @@
         <v>80</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="Y80" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="Y80" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="Z80" t="s" s="2">
-        <v>499</v>
+        <v>80</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>80</v>
@@ -11234,13 +11361,13 @@
         <v>80</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>496</v>
+        <v>506</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>80</v>
@@ -11252,21 +11379,21 @@
         <v>80</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>500</v>
+        <v>511</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>501</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="81" hidden="true">
+    <row r="81">
       <c r="A81" t="s" s="2">
-        <v>502</v>
+        <v>512</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>502</v>
+        <v>512</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11280,7 +11407,7 @@
         <v>88</v>
       </c>
       <c r="H81" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I81" t="s" s="2">
         <v>80</v>
@@ -11289,15 +11416,17 @@
         <v>80</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>203</v>
+        <v>295</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>503</v>
+        <v>513</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="N81" s="2"/>
+        <v>514</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>515</v>
+      </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>80</v>
@@ -11322,13 +11451,13 @@
         <v>80</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>301</v>
+        <v>80</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>505</v>
+        <v>80</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>506</v>
+        <v>80</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>80</v>
@@ -11346,7 +11475,7 @@
         <v>80</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>502</v>
+        <v>512</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
@@ -11364,21 +11493,21 @@
         <v>80</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>186</v>
+        <v>516</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>507</v>
+        <v>80</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>508</v>
+        <v>517</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>508</v>
+        <v>517</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11389,7 +11518,7 @@
         <v>78</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>80</v>
@@ -11401,20 +11530,16 @@
         <v>80</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>203</v>
+        <v>102</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>509</v>
+        <v>103</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>510</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="O82" t="s" s="2">
-        <v>512</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="N82" s="2"/>
+      <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>80</v>
       </c>
@@ -11438,13 +11563,13 @@
         <v>80</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>301</v>
+        <v>80</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>513</v>
+        <v>80</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>514</v>
+        <v>80</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>80</v>
@@ -11462,39 +11587,39 @@
         <v>80</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>508</v>
+        <v>105</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>515</v>
+        <v>106</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>516</v>
+        <v>80</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11517,13 +11642,13 @@
         <v>80</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>203</v>
+        <v>109</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>519</v>
+        <v>190</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -11550,31 +11675,29 @@
         <v>80</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>112</v>
+        <v>80</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>520</v>
+        <v>80</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>521</v>
+        <v>80</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AB83" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC83" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="AC83" s="2"/>
       <c r="AD83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE83" t="s" s="2">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>517</v>
+        <v>116</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
@@ -11586,29 +11709,31 @@
         <v>80</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>522</v>
+        <v>80</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>523</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="84" hidden="true">
+    <row r="84">
       <c r="A84" t="s" s="2">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="C84" s="2"/>
+        <v>518</v>
+      </c>
+      <c r="C84" t="s" s="2">
+        <v>521</v>
+      </c>
       <c r="D84" t="s" s="2">
         <v>80</v>
       </c>
@@ -11617,10 +11742,10 @@
         <v>78</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H84" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I84" t="s" s="2">
         <v>80</v>
@@ -11629,13 +11754,13 @@
         <v>80</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>203</v>
+        <v>522</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -11662,13 +11787,13 @@
         <v>80</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>112</v>
+        <v>80</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>527</v>
+        <v>80</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>528</v>
+        <v>80</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>80</v>
@@ -11686,7 +11811,7 @@
         <v>80</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>524</v>
+        <v>116</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
@@ -11695,62 +11820,66 @@
         <v>79</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>80</v>
+        <v>197</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>529</v>
+        <v>80</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>530</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>531</v>
+        <v>524</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>531</v>
+        <v>524</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>80</v>
+        <v>302</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I85" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="I85" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="J85" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>492</v>
+        <v>109</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>532</v>
+        <v>303</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="N85" s="2"/>
-      <c r="O85" s="2"/>
+        <v>304</v>
+      </c>
+      <c r="N85" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="O85" t="s" s="2">
+        <v>221</v>
+      </c>
       <c r="P85" t="s" s="2">
         <v>80</v>
       </c>
@@ -11798,39 +11927,39 @@
         <v>80</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>531</v>
+        <v>305</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>534</v>
+        <v>187</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>535</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>536</v>
+        <v>525</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>536</v>
+        <v>525</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11844,7 +11973,7 @@
         <v>88</v>
       </c>
       <c r="H86" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="I86" t="s" s="2">
         <v>80</v>
@@ -11853,13 +11982,13 @@
         <v>80</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>203</v>
+        <v>224</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>537</v>
+        <v>526</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>538</v>
+        <v>527</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -11886,11 +12015,13 @@
         <v>80</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="Y86" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="Z86" t="s" s="2">
-        <v>539</v>
+        <v>80</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>80</v>
@@ -11908,7 +12039,7 @@
         <v>80</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>536</v>
+        <v>525</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
@@ -11926,21 +12057,21 @@
         <v>80</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>540</v>
+        <v>228</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>541</v>
+        <v>528</v>
       </c>
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>542</v>
+        <v>529</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>542</v>
+        <v>529</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11951,7 +12082,7 @@
         <v>78</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>80</v>
@@ -11963,17 +12094,15 @@
         <v>80</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>255</v>
+        <v>530</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>543</v>
+        <v>531</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>545</v>
-      </c>
+        <v>532</v>
+      </c>
+      <c r="N87" s="2"/>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>80</v>
@@ -12022,13 +12151,13 @@
         <v>80</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>542</v>
+        <v>529</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>80</v>
@@ -12040,7 +12169,7 @@
         <v>80</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>546</v>
+        <v>533</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>80</v>
@@ -12049,12 +12178,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="88" hidden="true">
+    <row r="88">
       <c r="A88" t="s" s="2">
-        <v>547</v>
+        <v>534</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>547</v>
+        <v>534</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12068,7 +12197,7 @@
         <v>88</v>
       </c>
       <c r="H88" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I88" t="s" s="2">
         <v>80</v>
@@ -12077,13 +12206,13 @@
         <v>80</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>182</v>
+        <v>244</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>183</v>
+        <v>535</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>184</v>
+        <v>536</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -12110,13 +12239,11 @@
         <v>80</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y88" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>238</v>
+      </c>
+      <c r="Y88" s="2"/>
       <c r="Z88" t="s" s="2">
-        <v>80</v>
+        <v>537</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>80</v>
@@ -12134,7 +12261,7 @@
         <v>80</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>185</v>
+        <v>534</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
@@ -12146,38 +12273,38 @@
         <v>80</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>186</v>
+        <v>538</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>80</v>
+        <v>539</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>548</v>
+        <v>540</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>548</v>
+        <v>540</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>167</v>
+        <v>80</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>80</v>
@@ -12189,17 +12316,15 @@
         <v>80</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>133</v>
+        <v>244</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>188</v>
+        <v>541</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>170</v>
-      </c>
+        <v>542</v>
+      </c>
+      <c r="N89" s="2"/>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>80</v>
@@ -12224,13 +12349,13 @@
         <v>80</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>80</v>
+        <v>154</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>80</v>
+        <v>543</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>80</v>
+        <v>544</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>80</v>
@@ -12248,43 +12373,43 @@
         <v>80</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>191</v>
+        <v>540</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>186</v>
+        <v>106</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>80</v>
+        <v>545</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>262</v>
+        <v>80</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
@@ -12297,25 +12422,25 @@
         <v>80</v>
       </c>
       <c r="I90" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>133</v>
+        <v>244</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>263</v>
+        <v>547</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>264</v>
+        <v>548</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>170</v>
+        <v>549</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>171</v>
+        <v>550</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>80</v>
@@ -12340,13 +12465,13 @@
         <v>80</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>80</v>
+        <v>154</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>80</v>
+        <v>551</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>80</v>
+        <v>552</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>80</v>
@@ -12364,7 +12489,7 @@
         <v>80</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>265</v>
+        <v>546</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
@@ -12376,27 +12501,27 @@
         <v>80</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>131</v>
+        <v>553</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>80</v>
+        <v>554</v>
       </c>
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12404,10 +12529,10 @@
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>80</v>
@@ -12419,13 +12544,13 @@
         <v>80</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>551</v>
+        <v>244</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -12452,13 +12577,13 @@
         <v>80</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>80</v>
+        <v>168</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>80</v>
+        <v>558</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>80</v>
+        <v>559</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>80</v>
@@ -12476,13 +12601,13 @@
         <v>80</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="AG91" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI91" t="s" s="2">
         <v>80</v>
@@ -12491,24 +12616,24 @@
         <v>100</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>554</v>
+        <v>80</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>369</v>
+        <v>560</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>555</v>
+        <v>80</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>556</v>
+        <v>561</v>
       </c>
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12519,7 +12644,7 @@
         <v>78</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>80</v>
@@ -12531,17 +12656,15 @@
         <v>80</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>108</v>
+        <v>244</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>560</v>
-      </c>
+        <v>564</v>
+      </c>
+      <c r="N92" s="2"/>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
         <v>80</v>
@@ -12566,37 +12689,37 @@
         <v>80</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>197</v>
+        <v>168</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="Z92" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="AA92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF92" t="s" s="2">
         <v>562</v>
       </c>
-      <c r="AA92" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB92" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC92" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD92" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE92" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF92" t="s" s="2">
-        <v>557</v>
-      </c>
       <c r="AG92" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>80</v>
@@ -12608,21 +12731,21 @@
         <v>80</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>80</v>
+        <v>568</v>
       </c>
     </row>
-    <row r="93" hidden="true">
+    <row r="93">
       <c r="A93" t="s" s="2">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12636,7 +12759,7 @@
         <v>88</v>
       </c>
       <c r="H93" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I93" t="s" s="2">
         <v>80</v>
@@ -12645,17 +12768,15 @@
         <v>80</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>203</v>
+        <v>570</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>567</v>
-      </c>
+        <v>572</v>
+      </c>
+      <c r="N93" s="2"/>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
         <v>80</v>
@@ -12680,31 +12801,31 @@
         <v>80</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>301</v>
+        <v>80</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>568</v>
+        <v>80</v>
       </c>
       <c r="Z93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF93" t="s" s="2">
         <v>569</v>
-      </c>
-      <c r="AA93" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB93" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC93" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD93" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE93" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF93" t="s" s="2">
-        <v>564</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
@@ -12722,21 +12843,21 @@
         <v>80</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>80</v>
+        <v>573</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>80</v>
+        <v>574</v>
       </c>
     </row>
-    <row r="94" hidden="true">
+    <row r="94">
       <c r="A94" t="s" s="2">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12750,7 +12871,7 @@
         <v>88</v>
       </c>
       <c r="H94" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I94" t="s" s="2">
         <v>80</v>
@@ -12759,13 +12880,13 @@
         <v>80</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>231</v>
+        <v>244</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -12792,13 +12913,11 @@
         <v>80</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y94" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>238</v>
+      </c>
+      <c r="Y94" s="2"/>
       <c r="Z94" t="s" s="2">
-        <v>80</v>
+        <v>578</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>80</v>
@@ -12816,7 +12935,7 @@
         <v>80</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
@@ -12834,21 +12953,21 @@
         <v>80</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>362</v>
+        <v>579</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>80</v>
+        <v>580</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>573</v>
+        <v>581</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>573</v>
+        <v>581</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12856,13 +12975,13 @@
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H95" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="I95" t="s" s="2">
         <v>80</v>
@@ -12871,15 +12990,17 @@
         <v>80</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>574</v>
+        <v>295</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>575</v>
+        <v>582</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>576</v>
-      </c>
-      <c r="N95" s="2"/>
+        <v>583</v>
+      </c>
+      <c r="N95" t="s" s="2">
+        <v>584</v>
+      </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>80</v>
@@ -12928,13 +13049,13 @@
         <v>80</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>573</v>
+        <v>581</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI95" t="s" s="2">
         <v>80</v>
@@ -12943,24 +13064,24 @@
         <v>100</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>368</v>
+        <v>80</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>577</v>
+        <v>585</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>578</v>
+        <v>80</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>579</v>
+        <v>586</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>579</v>
+        <v>586</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -12983,17 +13104,15 @@
         <v>80</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>580</v>
+        <v>102</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>581</v>
+        <v>103</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>583</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="N96" s="2"/>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
         <v>80</v>
@@ -13042,7 +13161,7 @@
         <v>80</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>579</v>
+        <v>105</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>78</v>
@@ -13054,23 +13173,931 @@
         <v>80</v>
       </c>
       <c r="AJ96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL96" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AM96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN96" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="97" hidden="true">
+      <c r="A97" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="B97" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="C97" s="2"/>
+      <c r="D97" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="E97" s="2"/>
+      <c r="F97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G97" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K97" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L97" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="M97" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="N97" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="O97" s="2"/>
+      <c r="P97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q97" s="2"/>
+      <c r="R97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF97" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AG97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH97" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ97" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="AK97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL97" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AM97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN97" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="98" hidden="true">
+      <c r="A98" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="B98" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="C98" s="2"/>
+      <c r="D98" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="E98" s="2"/>
+      <c r="F98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G98" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I98" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="J98" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K98" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L98" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="M98" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="N98" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="O98" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="P98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q98" s="2"/>
+      <c r="R98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF98" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="AG98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH98" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ98" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="AK98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL98" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="AM98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN98" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="99" hidden="true">
+      <c r="A99" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="B99" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="C99" s="2"/>
+      <c r="D99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E99" s="2"/>
+      <c r="F99" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G99" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K99" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="L99" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="M99" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="N99" s="2"/>
+      <c r="O99" s="2"/>
+      <c r="P99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q99" s="2"/>
+      <c r="R99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF99" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="AG99" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH99" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ99" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AK96" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="AL96" t="s" s="2">
-        <v>585</v>
-      </c>
-      <c r="AM96" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN96" t="s" s="2">
+      <c r="AK99" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="AL99" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="AM99" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="AN99" t="s" s="2">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="100" hidden="true">
+      <c r="A100" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="B100" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="C100" s="2"/>
+      <c r="D100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E100" s="2"/>
+      <c r="F100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G100" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K100" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="L100" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="M100" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="N100" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="O100" s="2"/>
+      <c r="P100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q100" s="2"/>
+      <c r="R100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X100" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="Y100" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="Z100" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="AA100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF100" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="AG100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH100" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ100" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL100" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="AM100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN100" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="101" hidden="true">
+      <c r="A101" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="B101" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="C101" s="2"/>
+      <c r="D101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E101" s="2"/>
+      <c r="F101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G101" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K101" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="L101" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="M101" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="N101" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="O101" s="2"/>
+      <c r="P101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q101" s="2"/>
+      <c r="R101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X101" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="Y101" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="Z101" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="AA101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF101" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="AG101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH101" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ101" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN101" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="102" hidden="true">
+      <c r="A102" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="B102" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="C102" s="2"/>
+      <c r="D102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E102" s="2"/>
+      <c r="F102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G102" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K102" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="L102" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="M102" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="N102" s="2"/>
+      <c r="O102" s="2"/>
+      <c r="P102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q102" s="2"/>
+      <c r="R102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF102" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="AG102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH102" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ102" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL102" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="AM102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN102" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="B103" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="C103" s="2"/>
+      <c r="D103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E103" s="2"/>
+      <c r="F103" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G103" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H103" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="I103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K103" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="L103" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="M103" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="N103" s="2"/>
+      <c r="O103" s="2"/>
+      <c r="P103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q103" s="2"/>
+      <c r="R103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF103" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="AG103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH103" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ103" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK103" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="AL103" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="AM103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN103" t="s" s="2">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="104" hidden="true">
+      <c r="A104" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="B104" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="C104" s="2"/>
+      <c r="D104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E104" s="2"/>
+      <c r="F104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G104" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K104" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="L104" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="M104" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="N104" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="O104" s="2"/>
+      <c r="P104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q104" s="2"/>
+      <c r="R104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF104" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="AG104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH104" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ104" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK104" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="AL104" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="AM104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN104" t="s" s="2">
         <v>80</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN96">
+  <autoFilter ref="A1:AN104">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -13080,7 +14107,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI95">
+  <conditionalFormatting sqref="A2:AI103">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
